--- a/2. Data Transmission/Self-Evaluation Checklist.xlsx
+++ b/2. Data Transmission/Self-Evaluation Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAMBRIDGE IGCSE &amp; O LEVEL COMPUTER SCIENCE\2. Data Transmission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F320A4C-80B1-490D-B7E2-2E8145A99033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812C440A-E7BE-4556-8BDF-8051CA8AB516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D7E211F7-CE04-42BE-8074-4878EF679188}"/>
   </bookViews>
@@ -35,8 +35,43 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anwar ullah Afridi</author>
+  </authors>
+  <commentList>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{2F042707-CF2B-420D-9F5D-A02262A31E56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anwar ullah Afridi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+4-wire half-duplex setup
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t xml:space="preserve">I can </t>
   </si>
@@ -96,13 +131,16 @@
   </si>
   <si>
     <t>Describe how data is encrypted using asymmetric encryption</t>
+  </si>
+  <si>
+    <t>●</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,8 +170,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,6 +206,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -180,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -189,6 +252,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -524,11 +590,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A1EC37-D931-45CA-8F87-386455A47F35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A1EC37-D931-45CA-8F87-386455A47F35}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="95.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="119.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.54296875" bestFit="1" customWidth="1"/>
@@ -561,7 +627,9 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="E2" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -572,7 +640,9 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -583,7 +653,9 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
@@ -594,7 +666,9 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -605,7 +679,9 @@
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="E6" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -616,7 +692,9 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -627,7 +705,9 @@
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="E8" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -638,7 +718,9 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
@@ -649,7 +731,9 @@
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="E10" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -660,7 +744,9 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="E11" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
@@ -671,7 +757,9 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="E12" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -682,7 +770,9 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="E13" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
@@ -693,7 +783,9 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="E14" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -704,7 +796,9 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="E15" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
@@ -715,10 +809,13 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>